--- a/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="导入模板" sheetId="2" r:id="rId1"/>
@@ -32,15 +32,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
   <si>
     <t>sku编码</t>
   </si>
   <si>
+    <t>产品名称</t>
+  </si>
+  <si>
     <t>EAN码</t>
-  </si>
-  <si>
-    <t>产品名称</t>
   </si>
   <si>
     <t>所属仓库</t>
@@ -78,6 +78,9 @@
   <si>
     <t>①文本框填入
 ②取《产品管理》所有sku编码</t>
+  </si>
+  <si>
+    <t>①由sku编码在《产品管理》带出“产品名称”</t>
   </si>
   <si>
     <t>①由sku在《产品管理》带出“EAN码”</t>
@@ -298,7 +301,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -316,6 +319,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -323,6 +333,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -709,12 +725,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -818,28 +849,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -848,162 +870,183 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1336,8 +1379,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="7"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.5714285714286" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
@@ -1353,13 +1396,13 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1371,12 +1414,18 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="2" ht="13.5" spans="1:8">
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" ht="13.5" spans="1:8">
+      <c r="B3" s="8"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="A1">
+  <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1390,20 +1439,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="7"/>
+  <dimension ref="A1:I200"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="29" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="21" width="10" customWidth="1"/>
+    <col min="2" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="29" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="10" max="22" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:9">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1412,87 +1461,97 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1" spans="1:8">
-      <c r="A2" s="10" t="s">
+    <row r="2" ht="26" customHeight="1" spans="1:9">
+      <c r="A2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="67" customHeight="1" spans="1:8">
-      <c r="A3" s="11" t="s">
+    <row r="3" ht="67" customHeight="1" spans="1:9">
+      <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="15" t="s">
         <v>20</v>
       </c>
+      <c r="I3" s="15" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" ht="170" customHeight="1" spans="1:8">
-      <c r="A4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="13" t="s">
+    <row r="4" ht="170" customHeight="1" spans="1:9">
+      <c r="A4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
     </row>
     <row r="5" ht="15" customHeight="1"/>
     <row r="6" ht="15" customHeight="1"/>
@@ -1692,7 +1751,7 @@
     <row r="200" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1705,140 +1764,147 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="7"/>
+  <dimension ref="A1:I200"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="70" customWidth="1"/>
-    <col min="9" max="21" width="10" customWidth="1"/>
+    <col min="1" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="70" customWidth="1"/>
+    <col min="10" max="22" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:8">
+    <row r="1" ht="23" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>23</v>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>24</v>
+      <c r="I1" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1" spans="1:8">
-      <c r="A2" s="6">
+    <row r="2" ht="42" customHeight="1" spans="1:9">
+      <c r="A2" s="7">
         <v>1602</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="8"/>
+      <c r="C2" s="7">
         <v>6943231232</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="7">
         <v>786093</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="7">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>28</v>
       </c>
+      <c r="I2" s="9" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="3" ht="36" customHeight="1" spans="1:8">
-      <c r="A3" s="8">
+    <row r="3" ht="36" customHeight="1" spans="1:9">
+      <c r="A3" s="10">
         <v>1601</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="11"/>
+      <c r="C3" s="10">
         <v>6943231232</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="10">
         <v>2</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:9">
+      <c r="A4" s="10">
+        <v>1601</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="10">
+        <v>6943231232</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>32</v>
+      <c r="G4" s="10">
+        <v>3</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:8">
-      <c r="A4" s="8">
+    <row r="5" ht="36" customHeight="1" spans="1:9">
+      <c r="A5" s="7">
         <v>1601</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B5" s="8"/>
+      <c r="C5" s="7">
         <v>6943231232</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="8">
-        <v>3</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:8">
-      <c r="A5" s="6">
-        <v>1601</v>
-      </c>
-      <c r="B5" s="6">
-        <v>6943231232</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="7">
         <v>4</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>27</v>
+      <c r="H5" s="12" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="导入模板" sheetId="2" r:id="rId1"/>
@@ -106,13 +106,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">一、整个表数据导入成功才更新覆盖，否则整个表导入失败；
 二、以“sku编码+推荐仓位”为key，排重：
 </t>
@@ -231,7 +224,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">sku+仓位在导入表中重复了，请调整（重复行提亮）
+      <t xml:space="preserve">sku+仓位在导入表中重复了，请调整
 </t>
     </r>
     <r>
@@ -343,6 +336,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -494,7 +494,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -502,18 +501,12 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,6 +515,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD8D8D8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -534,7 +533,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9DBDE"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,70 +848,67 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -927,90 +923,96 @@
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1025,11 +1027,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1045,6 +1050,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1390,36 +1398,36 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="13.5" spans="1:8">
-      <c r="B2" s="8"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" ht="13.5" spans="1:8">
-      <c r="B3" s="8"/>
+      <c r="B3" s="9"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1" etc:filterBottomFollowUsedRange="0">
@@ -1452,106 +1460,106 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" ht="67" customHeight="1" spans="1:9">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" ht="170" customHeight="1" spans="1:9">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
     </row>
     <row r="5" ht="15" customHeight="1"/>
     <row r="6" ht="15" customHeight="1"/>
@@ -1774,136 +1782,136 @@
   </cols>
   <sheetData>
     <row r="1" ht="23" customHeight="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:9">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1602</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="7">
+      <c r="B2" s="9"/>
+      <c r="C2" s="8">
         <v>6943231232</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>786093</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>1</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" spans="1:9">
-      <c r="A3" s="10">
+    <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A3" s="11">
         <v>1601</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="10">
+      <c r="B3" s="12"/>
+      <c r="C3" s="11">
         <v>6943231232</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="11">
         <v>2</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:9">
-      <c r="A4" s="10">
+    <row r="4" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
+      <c r="A4" s="11">
         <v>1601</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="10">
+      <c r="B4" s="12"/>
+      <c r="C4" s="11">
         <v>6943231232</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="11">
         <v>3</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:9">
-      <c r="A5" s="7">
+      <c r="A5" s="8">
         <v>1601</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="7">
+      <c r="B5" s="9"/>
+      <c r="C5" s="8">
         <v>6943231232</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <v>4</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="14" t="s">
         <v>28</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -32,15 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>sku编码</t>
   </si>
   <si>
     <t>产品名称</t>
-  </si>
-  <si>
-    <t>EAN码</t>
   </si>
   <si>
     <t>所属仓库</t>
@@ -81,9 +78,6 @@
   </si>
   <si>
     <t>①由sku编码在《产品管理》带出“产品名称”</t>
-  </si>
-  <si>
-    <t>①由sku在《产品管理》带出“EAN码”</t>
   </si>
   <si>
     <t>①填写“执行仓库”</t>
@@ -1383,18 +1377,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.5714285714286" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="22" width="10" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="7" max="21" width="10" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:8">
@@ -1404,13 +1399,13 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -1418,9 +1413,6 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" ht="13.5" spans="1:8">
@@ -1430,7 +1422,7 @@
       <c r="B3" s="9"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:G1" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A1:B1">
@@ -1443,25 +1435,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="29" customWidth="1"/>
-    <col min="9" max="9" width="23" customWidth="1"/>
-    <col min="10" max="22" width="10" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="21" width="10" customWidth="1"/>
+    <col min="2" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1469,13 +1461,13 @@
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1483,75 +1475,66 @@
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9">
       <c r="A2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="67" customHeight="1" spans="1:9">
       <c r="A3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="E3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="F3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="G3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="H3" s="17" t="s">
         <v>19</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" ht="170" customHeight="1" spans="1:9">
       <c r="A4" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -1559,7 +1542,6 @@
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
     </row>
     <row r="5" ht="15" customHeight="1"/>
     <row r="6" ht="15" customHeight="1"/>
@@ -1759,7 +1741,7 @@
     <row r="200" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B4:H4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1768,17 +1750,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="70" customWidth="1"/>
-    <col min="10" max="22" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
+    <col min="9" max="21" width="10" customWidth="1"/>
+    <col min="1" max="2" width="17" customWidth="1"/>
+    <col min="3" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="23" customHeight="1" spans="1:9">
@@ -1789,25 +1772,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>25</v>
+      <c r="H1" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:9">
@@ -1815,26 +1795,23 @@
         <v>1602</v>
       </c>
       <c r="B2" s="9"/>
-      <c r="C2" s="8">
-        <v>6943231232</v>
+      <c r="C2" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="8">
+        <v>786093</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>27</v>
-      </c>
-      <c r="F2" s="8">
-        <v>786093</v>
-      </c>
-      <c r="G2" s="8">
-        <v>1</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
@@ -1842,26 +1819,23 @@
         <v>1601</v>
       </c>
       <c r="B3" s="12"/>
-      <c r="C3" s="11">
-        <v>6943231232</v>
+      <c r="C3" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="11">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="G3" s="11">
-        <v>2</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
@@ -1869,26 +1843,23 @@
         <v>1601</v>
       </c>
       <c r="B4" s="12"/>
-      <c r="C4" s="11">
-        <v>6943231232</v>
+      <c r="C4" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="D4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="11">
+        <v>3</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="11" t="s">
+      <c r="H4" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" s="11">
-        <v>3</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:9">
@@ -1896,23 +1867,20 @@
         <v>1601</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="8">
-        <v>6943231232</v>
+      <c r="C5" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="8">
+        <v>4</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>26</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="8">
-        <v>4</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="导入模板" sheetId="2" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="导入报错样式" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">导入模板!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">导入模板!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -100,6 +100,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">一、整个表数据导入成功才更新覆盖，否则整个表导入失败；
 二、以“sku编码+推荐仓位”为key，排重：
 </t>
@@ -500,7 +507,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,12 +529,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,7 +864,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -887,16 +888,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -905,85 +906,85 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1021,10 +1022,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1377,22 +1378,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.5714285714286" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="6" width="14" customWidth="1"/>
     <col min="7" max="21" width="10" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:8">
+    <row r="1" ht="24" customHeight="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1415,14 +1415,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="13.5" spans="1:8">
+    <row r="2" ht="13.5" spans="1:7">
       <c r="B2" s="9"/>
     </row>
-    <row r="3" ht="13.5" spans="1:8">
+    <row r="3" ht="13.5" spans="1:7">
       <c r="B3" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G1" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A1:B1">
@@ -1435,23 +1435,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="6" width="24" customWidth="1"/>
     <col min="7" max="7" width="29" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
     <col min="9" max="21" width="10" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:9">
+    <row r="1" ht="26" customHeight="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1" spans="1:9">
+    <row r="2" ht="26" customHeight="1" spans="1:8">
       <c r="A2" s="15" t="s">
         <v>9</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="67" customHeight="1" spans="1:9">
+    <row r="3" ht="67" customHeight="1" spans="1:8">
       <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="170" customHeight="1" spans="1:9">
+    <row r="4" ht="170" customHeight="1" spans="1:8">
       <c r="A4" s="15" t="s">
         <v>20</v>
       </c>
@@ -1750,21 +1750,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="70" customWidth="1"/>
     <col min="9" max="21" width="10" customWidth="1"/>
-    <col min="1" max="2" width="17" customWidth="1"/>
-    <col min="3" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:9">
+    <row r="1" ht="23" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +1789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1" spans="1:9">
+    <row r="2" ht="42" customHeight="1" spans="1:8">
       <c r="A2" s="8">
         <v>1602</v>
       </c>
@@ -1814,7 +1813,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:8">
       <c r="A3" s="11">
         <v>1601</v>
       </c>
@@ -1838,7 +1837,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="36" customHeight="1" spans="1:8">
       <c r="A4" s="11">
         <v>1601</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" spans="1:9">
+    <row r="5" ht="36" customHeight="1" spans="1:8">
       <c r="A5" s="8">
         <v>1601</v>
       </c>

--- a/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="导入模板" sheetId="2" r:id="rId1"/>
     <sheet name="导入填写指南" sheetId="3" r:id="rId2"/>
-    <sheet name="导入报错样式" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">导入模板!$A$1:$G$1</definedName>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>sku编码</t>
   </si>
@@ -247,43 +246,6 @@
       <t>无法识别状态选择，仅可填“启用/禁用”</t>
     </r>
   </si>
-  <si>
-    <t>执行仓库</t>
-  </si>
-  <si>
-    <t>报错说明</t>
-  </si>
-  <si>
-    <t>东莞售后仓</t>
-  </si>
-  <si>
-    <t>拣货区</t>
-  </si>
-  <si>
-    <t>启用</t>
-  </si>
-  <si>
-    <t>无法识别sku，请确定sku编码是否正确
-未能找到仓库仓位，请确定仓位是否正确</t>
-  </si>
-  <si>
-    <t>A区</t>
-  </si>
-  <si>
-    <t>3B6093</t>
-  </si>
-  <si>
-    <t>禁用</t>
-  </si>
-  <si>
-    <t>sku+仓位在导入表中重复了，请调整</t>
-  </si>
-  <si>
-    <t>B区</t>
-  </si>
-  <si>
-    <t>2A86093</t>
-  </si>
 </sst>
 </file>
 
@@ -306,6 +268,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -314,13 +283,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -507,18 +469,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -864,7 +820,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -888,16 +844,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -906,112 +862,106 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1019,25 +969,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1049,7 +981,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1402,7 +1334,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1416,10 +1348,10 @@
       </c>
     </row>
     <row r="2" ht="13.5" spans="1:7">
-      <c r="B2" s="9"/>
+      <c r="B2" s="7"/>
     </row>
     <row r="3" ht="13.5" spans="1:7">
-      <c r="B3" s="9"/>
+      <c r="B3" s="7"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G1" etc:filterBottomFollowUsedRange="0">
@@ -1452,7 +1384,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1464,7 +1396,7 @@
       <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -1478,70 +1410,70 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:8">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="67" customHeight="1" spans="1:8">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" ht="170" customHeight="1" spans="1:8">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" ht="15" customHeight="1"/>
     <row r="6" ht="15" customHeight="1"/>
@@ -1747,339 +1679,4 @@
   <headerFooter/>
   <picture r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="70" customWidth="1"/>
-    <col min="9" max="21" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1" spans="1:8">
-      <c r="A2" s="8">
-        <v>1602</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="8">
-        <v>786093</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="36" customHeight="1" spans="1:8">
-      <c r="A3" s="11">
-        <v>1601</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="11">
-        <v>2</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="36" customHeight="1" spans="1:8">
-      <c r="A4" s="11">
-        <v>1601</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="11">
-        <v>3</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:8">
-      <c r="A5" s="8">
-        <v>1601</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="8">
-        <v>4</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1"/>
-    <row r="7" ht="15" customHeight="1"/>
-    <row r="8" ht="15" customHeight="1"/>
-    <row r="9" ht="15" customHeight="1"/>
-    <row r="10" ht="15" customHeight="1"/>
-    <row r="11" ht="15" customHeight="1"/>
-    <row r="12" ht="15" customHeight="1"/>
-    <row r="13" ht="15" customHeight="1"/>
-    <row r="14" ht="15" customHeight="1"/>
-    <row r="15" ht="15" customHeight="1"/>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="15" customHeight="1"/>
-    <row r="19" ht="15" customHeight="1"/>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="15" customHeight="1"/>
-    <row r="26" ht="15" customHeight="1"/>
-    <row r="27" ht="15" customHeight="1"/>
-    <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="15" customHeight="1"/>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="43" ht="15" customHeight="1"/>
-    <row r="44" ht="15" customHeight="1"/>
-    <row r="45" ht="15" customHeight="1"/>
-    <row r="46" ht="15" customHeight="1"/>
-    <row r="47" ht="15" customHeight="1"/>
-    <row r="48" ht="15" customHeight="1"/>
-    <row r="49" ht="15" customHeight="1"/>
-    <row r="50" ht="15" customHeight="1"/>
-    <row r="51" ht="15" customHeight="1"/>
-    <row r="52" ht="15" customHeight="1"/>
-    <row r="53" ht="15" customHeight="1"/>
-    <row r="54" ht="15" customHeight="1"/>
-    <row r="55" ht="15" customHeight="1"/>
-    <row r="56" ht="15" customHeight="1"/>
-    <row r="57" ht="15" customHeight="1"/>
-    <row r="58" ht="15" customHeight="1"/>
-    <row r="59" ht="15" customHeight="1"/>
-    <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="15" customHeight="1"/>
-    <row r="62" ht="15" customHeight="1"/>
-    <row r="63" ht="15" customHeight="1"/>
-    <row r="64" ht="15" customHeight="1"/>
-    <row r="65" ht="15" customHeight="1"/>
-    <row r="66" ht="15" customHeight="1"/>
-    <row r="67" ht="15" customHeight="1"/>
-    <row r="68" ht="15" customHeight="1"/>
-    <row r="69" ht="15" customHeight="1"/>
-    <row r="70" ht="15" customHeight="1"/>
-    <row r="71" ht="15" customHeight="1"/>
-    <row r="72" ht="15" customHeight="1"/>
-    <row r="73" ht="15" customHeight="1"/>
-    <row r="74" ht="15" customHeight="1"/>
-    <row r="75" ht="15" customHeight="1"/>
-    <row r="76" ht="15" customHeight="1"/>
-    <row r="77" ht="15" customHeight="1"/>
-    <row r="78" ht="15" customHeight="1"/>
-    <row r="79" ht="15" customHeight="1"/>
-    <row r="80" ht="15" customHeight="1"/>
-    <row r="81" ht="15" customHeight="1"/>
-    <row r="82" ht="15" customHeight="1"/>
-    <row r="83" ht="15" customHeight="1"/>
-    <row r="84" ht="15" customHeight="1"/>
-    <row r="85" ht="15" customHeight="1"/>
-    <row r="86" ht="15" customHeight="1"/>
-    <row r="87" ht="15" customHeight="1"/>
-    <row r="88" ht="15" customHeight="1"/>
-    <row r="89" ht="15" customHeight="1"/>
-    <row r="90" ht="15" customHeight="1"/>
-    <row r="91" ht="15" customHeight="1"/>
-    <row r="92" ht="15" customHeight="1"/>
-    <row r="93" ht="15" customHeight="1"/>
-    <row r="94" ht="15" customHeight="1"/>
-    <row r="95" ht="15" customHeight="1"/>
-    <row r="96" ht="15" customHeight="1"/>
-    <row r="97" ht="15" customHeight="1"/>
-    <row r="98" ht="15" customHeight="1"/>
-    <row r="99" ht="15" customHeight="1"/>
-    <row r="100" ht="15" customHeight="1"/>
-    <row r="101" ht="15" customHeight="1"/>
-    <row r="102" ht="15" customHeight="1"/>
-    <row r="103" ht="15" customHeight="1"/>
-    <row r="104" ht="15" customHeight="1"/>
-    <row r="105" ht="15" customHeight="1"/>
-    <row r="106" ht="15" customHeight="1"/>
-    <row r="107" ht="15" customHeight="1"/>
-    <row r="108" ht="15" customHeight="1"/>
-    <row r="109" ht="15" customHeight="1"/>
-    <row r="110" ht="15" customHeight="1"/>
-    <row r="111" ht="15" customHeight="1"/>
-    <row r="112" ht="15" customHeight="1"/>
-    <row r="113" ht="15" customHeight="1"/>
-    <row r="114" ht="15" customHeight="1"/>
-    <row r="115" ht="15" customHeight="1"/>
-    <row r="116" ht="15" customHeight="1"/>
-    <row r="117" ht="15" customHeight="1"/>
-    <row r="118" ht="15" customHeight="1"/>
-    <row r="119" ht="15" customHeight="1"/>
-    <row r="120" ht="15" customHeight="1"/>
-    <row r="121" ht="15" customHeight="1"/>
-    <row r="122" ht="15" customHeight="1"/>
-    <row r="123" ht="15" customHeight="1"/>
-    <row r="124" ht="15" customHeight="1"/>
-    <row r="125" ht="15" customHeight="1"/>
-    <row r="126" ht="15" customHeight="1"/>
-    <row r="127" ht="15" customHeight="1"/>
-    <row r="128" ht="15" customHeight="1"/>
-    <row r="129" ht="15" customHeight="1"/>
-    <row r="130" ht="15" customHeight="1"/>
-    <row r="131" ht="15" customHeight="1"/>
-    <row r="132" ht="15" customHeight="1"/>
-    <row r="133" ht="15" customHeight="1"/>
-    <row r="134" ht="15" customHeight="1"/>
-    <row r="135" ht="15" customHeight="1"/>
-    <row r="136" ht="15" customHeight="1"/>
-    <row r="137" ht="15" customHeight="1"/>
-    <row r="138" ht="15" customHeight="1"/>
-    <row r="139" ht="15" customHeight="1"/>
-    <row r="140" ht="15" customHeight="1"/>
-    <row r="141" ht="15" customHeight="1"/>
-    <row r="142" ht="15" customHeight="1"/>
-    <row r="143" ht="15" customHeight="1"/>
-    <row r="144" ht="15" customHeight="1"/>
-    <row r="145" ht="15" customHeight="1"/>
-    <row r="146" ht="15" customHeight="1"/>
-    <row r="147" ht="15" customHeight="1"/>
-    <row r="148" ht="15" customHeight="1"/>
-    <row r="149" ht="15" customHeight="1"/>
-    <row r="150" ht="15" customHeight="1"/>
-    <row r="151" ht="15" customHeight="1"/>
-    <row r="152" ht="15" customHeight="1"/>
-    <row r="153" ht="15" customHeight="1"/>
-    <row r="154" ht="15" customHeight="1"/>
-    <row r="155" ht="15" customHeight="1"/>
-    <row r="156" ht="15" customHeight="1"/>
-    <row r="157" ht="15" customHeight="1"/>
-    <row r="158" ht="15" customHeight="1"/>
-    <row r="159" ht="15" customHeight="1"/>
-    <row r="160" ht="15" customHeight="1"/>
-    <row r="161" ht="15" customHeight="1"/>
-    <row r="162" ht="15" customHeight="1"/>
-    <row r="163" ht="15" customHeight="1"/>
-    <row r="164" ht="15" customHeight="1"/>
-    <row r="165" ht="15" customHeight="1"/>
-    <row r="166" ht="15" customHeight="1"/>
-    <row r="167" ht="15" customHeight="1"/>
-    <row r="168" ht="15" customHeight="1"/>
-    <row r="169" ht="15" customHeight="1"/>
-    <row r="170" ht="15" customHeight="1"/>
-    <row r="171" ht="15" customHeight="1"/>
-    <row r="172" ht="15" customHeight="1"/>
-    <row r="173" ht="15" customHeight="1"/>
-    <row r="174" ht="15" customHeight="1"/>
-    <row r="175" ht="15" customHeight="1"/>
-    <row r="176" ht="15" customHeight="1"/>
-    <row r="177" ht="15" customHeight="1"/>
-    <row r="178" ht="15" customHeight="1"/>
-    <row r="179" ht="15" customHeight="1"/>
-    <row r="180" ht="15" customHeight="1"/>
-    <row r="181" ht="15" customHeight="1"/>
-    <row r="182" ht="15" customHeight="1"/>
-    <row r="183" ht="15" customHeight="1"/>
-    <row r="184" ht="15" customHeight="1"/>
-    <row r="185" ht="15" customHeight="1"/>
-    <row r="186" ht="15" customHeight="1"/>
-    <row r="187" ht="15" customHeight="1"/>
-    <row r="188" ht="15" customHeight="1"/>
-    <row r="189" ht="15" customHeight="1"/>
-    <row r="190" ht="15" customHeight="1"/>
-    <row r="191" ht="15" customHeight="1"/>
-    <row r="192" ht="15" customHeight="1"/>
-    <row r="193" ht="15" customHeight="1"/>
-    <row r="194" ht="15" customHeight="1"/>
-    <row r="195" ht="15" customHeight="1"/>
-    <row r="196" ht="15" customHeight="1"/>
-    <row r="197" ht="15" customHeight="1"/>
-    <row r="198" ht="15" customHeight="1"/>
-    <row r="199" ht="15" customHeight="1"/>
-    <row r="200" ht="15" customHeight="1"/>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <picture r:id="rId1"/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/afterSalesWarehouseLocationSuggestExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="导入模板" sheetId="2" r:id="rId1"/>
